--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129679787</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129679771</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129679783</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129679787</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129679771</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129679783</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129679787</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129679771</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129679783</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129679787</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129679771</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129679783</v>
       </c>
       <c r="B4" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129679787</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49607-2025 artfynd.xlsx
+++ b/artfynd/A 49607-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129679787</v>
+        <v>129679771</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581574</v>
+        <v>581554</v>
       </c>
       <c r="R2" t="n">
-        <v>6400619</v>
+        <v>6400637</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,32 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129679771</v>
+        <v>129679783</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,11 +824,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581554</v>
+        <v>581574</v>
       </c>
       <c r="R3" t="n">
-        <v>6400637</v>
+        <v>6400619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 fruktkroppar på tall</t>
+          <t>Drog iväg från tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129679783</v>
+        <v>129679787</v>
       </c>
       <c r="B4" t="n">
-        <v>56930</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,7 +934,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,11 +982,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Drog iväg från tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
